--- a/excel_upload_masters/templates/08_sla.xlsx
+++ b/excel_upload_masters/templates/08_sla.xlsx
@@ -4,11 +4,12 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metric_definitions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sla_performances" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metric_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sla_performances" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,6 +434,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RAG_G</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RAG_A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RAG_R</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -553,7 +624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -632,7 +703,11 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Date/datetime — ISO-8601 or Excel date</t>
@@ -647,6 +722,11 @@
       <c r="J2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F3:F5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$A$1:$A$8</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>